--- a/age_distribution_calculations.xlsx
+++ b/age_distribution_calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3035ECA-D6B7-465D-980E-4C183A1FC155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E3035ECA-D6B7-465D-980E-4C183A1FC155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20DCAEF3-62FD-45D9-AABB-9E4AF6A23220}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="3156" windowWidth="17280" windowHeight="8880" xr2:uid="{2A79630C-9A4B-4DF8-A985-C83D0C0CC4DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A79630C-9A4B-4DF8-A985-C83D0C0CC4DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Total</t>
   </si>
@@ -58,19 +58,117 @@
   </si>
   <si>
     <t>percentage</t>
+  </si>
+  <si>
+    <t>Age Group</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Young (0-14)</t>
+  </si>
+  <si>
+    <t>Working Age (15-64)</t>
+  </si>
+  <si>
+    <t>Elderly (65+)</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
+    <t>25-29</t>
+  </si>
+  <si>
+    <t>30-34</t>
+  </si>
+  <si>
+    <t>35-39</t>
+  </si>
+  <si>
+    <t>40-44</t>
+  </si>
+  <si>
+    <t>45-49</t>
+  </si>
+  <si>
+    <t>50-54</t>
+  </si>
+  <si>
+    <t>55-59</t>
+  </si>
+  <si>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
+  </si>
+  <si>
+    <t>70-74</t>
+  </si>
+  <si>
+    <t>75-79</t>
+  </si>
+  <si>
+    <t>80-84</t>
+  </si>
+  <si>
+    <t>85 and over</t>
+  </si>
+  <si>
+    <t>Age Category</t>
+  </si>
+  <si>
+    <t>Population</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,15 +188,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{AB154E9D-9C31-40EC-90AB-A1666AE5D3D7}"/>
+    <cellStyle name="Normal 2 3" xfId="4" xr:uid="{22D396CA-C64C-4CC8-8B13-3FE25711AD16}"/>
+    <cellStyle name="Normal 3 2" xfId="1" xr:uid="{F992C03B-39F2-4DD8-988F-80745BA3F2B7}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{C2E26479-4674-4650-A523-463E46000F97}"/>
+    <cellStyle name="Normal 5" xfId="2" xr:uid="{85B7299B-B956-470E-BB74-4922D09FD137}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -532,13 +649,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE1C755-BF14-4727-B2D5-3664F9595416}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="25.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -548,8 +671,23 @@
       <c r="D1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -563,8 +701,24 @@
       <c r="D2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1">
+        <f>SUM([1]Sheet1!B2:B4)</f>
+        <v>4794908</v>
+      </c>
+      <c r="I2">
+        <v>2025</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1249765</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -579,8 +733,24 @@
       <c r="D3">
         <v>17.63</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
+        <f>SUM([1]Sheet1!B5:B14)</f>
+        <v>17701331</v>
+      </c>
+      <c r="I3">
+        <v>2025</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1246436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -595,8 +765,24 @@
       <c r="D4">
         <v>65.099999999999994</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1">
+        <f>SUM([1]Sheet1!B15:B22)</f>
+        <v>4697551</v>
+      </c>
+      <c r="I4">
+        <v>2025</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1251076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -611,6 +797,157 @@
       <c r="D5">
         <v>17.3</v>
       </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <f>SUM(M2:M4)</f>
+        <v>3747277</v>
+      </c>
+      <c r="I5">
+        <v>1971</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1136296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <f>SUM(M5:M14)</f>
+        <v>8229615</v>
+      </c>
+      <c r="I6">
+        <v>1971</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1140607</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <f>SUM(M15:M19)</f>
+        <v>1090373</v>
+      </c>
+      <c r="I7">
+        <v>1971</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="3">
+        <v>962394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="3">
+        <v>823969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="3">
+        <v>754860</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="3">
+        <v>803426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="3">
+        <v>797844</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="3">
+        <v>677510</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="3">
+        <v>616496</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="3">
+        <v>516213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="3">
+        <v>399031</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="3">
+        <v>298986</v>
+      </c>
+    </row>
+    <row r="17" spans="12:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="3">
+        <v>203537</v>
+      </c>
+    </row>
+    <row r="18" spans="12:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="3">
+        <v>121889</v>
+      </c>
+    </row>
+    <row r="19" spans="12:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="3">
+        <v>66930</v>
+      </c>
+    </row>
+    <row r="20" spans="12:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
